--- a/analysis/data/annotation/[Archived] Labeling SDG 9 - Benchmarking Dataset.xlsx
+++ b/analysis/data/annotation/[Archived] Labeling SDG 9 - Benchmarking Dataset.xlsx
@@ -12051,7 +12051,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="2" hidden="1">
+    <row r="2">
       <c r="A2" s="12" t="s">
         <v>216</v>
       </c>
@@ -12176,7 +12176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" hidden="1">
+    <row r="5">
       <c r="A5" s="12" t="s">
         <v>128</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" hidden="1">
+    <row r="9">
       <c r="A9" s="12" t="s">
         <v>220</v>
       </c>
@@ -12387,7 +12387,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="10" hidden="1">
+    <row r="10">
       <c r="A10" s="12" t="s">
         <v>152</v>
       </c>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" hidden="1">
+    <row r="13">
       <c r="A13" s="12" t="s">
         <v>91</v>
       </c>
@@ -12557,7 +12557,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="14" hidden="1">
+    <row r="14">
       <c r="A14" s="12" t="s">
         <v>282</v>
       </c>
@@ -12766,7 +12766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" hidden="1">
+    <row r="19">
       <c r="A19" s="12" t="s">
         <v>204</v>
       </c>
@@ -12811,7 +12811,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="20" hidden="1">
+    <row r="20">
       <c r="A20" s="12" t="s">
         <v>236</v>
       </c>
@@ -12938,7 +12938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" hidden="1">
+    <row r="23">
       <c r="A23" s="12" t="s">
         <v>120</v>
       </c>
@@ -12981,7 +12981,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="24" hidden="1">
+    <row r="24">
       <c r="A24" s="12" t="s">
         <v>238</v>
       </c>
@@ -13110,7 +13110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" hidden="1">
+    <row r="27">
       <c r="A27" s="12" t="s">
         <v>85</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="28" hidden="1">
+    <row r="28">
       <c r="A28" s="12" t="s">
         <v>172</v>
       </c>
@@ -13198,7 +13198,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="29" hidden="1">
+    <row r="29">
       <c r="A29" s="12" t="s">
         <v>198</v>
       </c>
@@ -13282,7 +13282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" hidden="1">
+    <row r="31">
       <c r="A31" s="12" t="s">
         <v>137</v>
       </c>
@@ -13407,7 +13407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" hidden="1">
+    <row r="34">
       <c r="A34" s="12" t="s">
         <v>186</v>
       </c>
@@ -13532,7 +13532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" hidden="1">
+    <row r="37">
       <c r="A37" s="12" t="s">
         <v>150</v>
       </c>
@@ -13575,7 +13575,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="38" hidden="1">
+    <row r="38">
       <c r="A38" s="12" t="s">
         <v>174</v>
       </c>
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" hidden="1">
+    <row r="41">
       <c r="A41" s="12" t="s">
         <v>200</v>
       </c>
@@ -13834,7 +13834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" hidden="1">
+    <row r="44">
       <c r="A44" s="12" t="s">
         <v>280</v>
       </c>
@@ -14045,7 +14045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" hidden="1">
+    <row r="49">
       <c r="A49" s="12" t="s">
         <v>95</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="50" hidden="1">
+    <row r="50">
       <c r="A50" s="12" t="s">
         <v>256</v>
       </c>
@@ -14129,7 +14129,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="51" hidden="1">
+    <row r="51">
       <c r="A51" s="12" t="s">
         <v>274</v>
       </c>
@@ -14172,7 +14172,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="52" hidden="1">
+    <row r="52">
       <c r="A52" s="12" t="s">
         <v>258</v>
       </c>
@@ -14295,7 +14295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" hidden="1">
+    <row r="55">
       <c r="A55" s="12" t="s">
         <v>170</v>
       </c>
@@ -14338,7 +14338,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="56" hidden="1">
+    <row r="56">
       <c r="A56" s="12" t="s">
         <v>290</v>
       </c>
@@ -14463,7 +14463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" hidden="1">
+    <row r="59">
       <c r="A59" s="12" t="s">
         <v>276</v>
       </c>
@@ -14506,7 +14506,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="60" hidden="1">
+    <row r="60">
       <c r="A60" s="12" t="s">
         <v>190</v>
       </c>
@@ -14549,7 +14549,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="61" hidden="1">
+    <row r="61">
       <c r="A61" s="12" t="s">
         <v>196</v>
       </c>
@@ -14720,7 +14720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" hidden="1">
+    <row r="65">
       <c r="A65" s="12" t="s">
         <v>232</v>
       </c>
@@ -14852,7 +14852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" hidden="1">
+    <row r="68">
       <c r="A68" s="12" t="s">
         <v>88</v>
       </c>
@@ -14979,7 +14979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" hidden="1">
+    <row r="71">
       <c r="A71" s="12" t="s">
         <v>272</v>
       </c>
@@ -15022,7 +15022,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="72" hidden="1">
+    <row r="72">
       <c r="A72" s="12" t="s">
         <v>126</v>
       </c>
@@ -15106,7 +15106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" hidden="1">
+    <row r="74">
       <c r="A74" s="12" t="s">
         <v>240</v>
       </c>
@@ -15190,7 +15190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" hidden="1">
+    <row r="76">
       <c r="A76" s="12" t="s">
         <v>278</v>
       </c>
@@ -15411,7 +15411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" hidden="1">
+    <row r="81">
       <c r="A81" s="12" t="s">
         <v>144</v>
       </c>
@@ -15452,7 +15452,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="82" hidden="1">
+    <row r="82">
       <c r="A82" s="12" t="s">
         <v>230</v>
       </c>
@@ -15577,7 +15577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" hidden="1">
+    <row r="85">
       <c r="A85" s="12" t="s">
         <v>178</v>
       </c>
@@ -15747,7 +15747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" hidden="1">
+    <row r="89">
       <c r="A89" s="12" t="s">
         <v>166</v>
       </c>
@@ -15790,7 +15790,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="90" hidden="1">
+    <row r="90">
       <c r="A90" s="12" t="s">
         <v>292</v>
       </c>
@@ -15924,7 +15924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" hidden="1">
+    <row r="93">
       <c r="A93" s="12" t="s">
         <v>267</v>
       </c>
@@ -15969,7 +15969,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="94" hidden="1">
+    <row r="94">
       <c r="A94" s="12" t="s">
         <v>146</v>
       </c>
@@ -16053,7 +16053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" hidden="1">
+    <row r="96">
       <c r="A96" s="12" t="s">
         <v>234</v>
       </c>
@@ -16217,7 +16217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" hidden="1">
+    <row r="100">
       <c r="A100" s="12" t="s">
         <v>242</v>
       </c>
@@ -16302,14 +16302,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$S$101">
-    <filterColumn colId="16">
-      <filters>
-        <filter val="TRUE"/>
-        <filter val="FALSE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="$A$1:$S$101"/>
   <conditionalFormatting sqref="C2:P101">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"TRUE"</formula>
